--- a/Analysis_parameters.xlsx
+++ b/Analysis_parameters.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dick\Post-doc\Analysis scripts\MS-basic-post-processing\All_tools\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dick\Post-doc\Github\MS-basic-post-processing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CBB2ED1-427D-468F-9BBD-D9BF3C1036B4}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADBA443F-FD5F-4064-9FB4-56FB5717BBFF}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="29925" yWindow="1125" windowWidth="28800" windowHeight="15345" xr2:uid="{5AB9C566-9F07-4C33-B851-369A57D17F28}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{5AB9C566-9F07-4C33-B851-369A57D17F28}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
@@ -526,7 +526,7 @@
         <v>7</v>
       </c>
       <c r="H2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I2" t="s">
         <v>13</v>

--- a/Analysis_parameters.xlsx
+++ b/Analysis_parameters.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dick\Post-doc\Github\MS-basic-post-processing\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dick\Post-doc\Analysis scripts\MS-basic-post-processing\All_tools\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADBA443F-FD5F-4064-9FB4-56FB5717BBFF}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E94234A-C42E-43CC-9770-AD9291750672}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{5AB9C566-9F07-4C33-B851-369A57D17F28}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="20">
   <si>
     <t>filtering_type</t>
   </si>
@@ -84,9 +84,6 @@
   </si>
   <si>
     <t>DiaNN</t>
-  </si>
-  <si>
-    <t>highlight_imputed</t>
   </si>
   <si>
     <t>contrasts</t>
@@ -447,7 +444,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79C10FB2-336F-4851-BC33-70582F98C0E5}">
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:M2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.85546875" bestFit="1" customWidth="1"/>
@@ -459,7 +456,7 @@
     <col min="7" max="7" width="7.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>15</v>
       </c>
@@ -476,7 +473,7 @@
         <v>2</v>
       </c>
       <c r="F1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G1" t="s">
         <v>3</v>
@@ -499,11 +496,8 @@
       <c r="M1" t="s">
         <v>13</v>
       </c>
-      <c r="N1" t="s">
-        <v>17</v>
-      </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -517,10 +511,10 @@
         <v>6</v>
       </c>
       <c r="E2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F2" t="s">
         <v>19</v>
-      </c>
-      <c r="F2" t="s">
-        <v>20</v>
       </c>
       <c r="G2" t="s">
         <v>7</v>
@@ -542,14 +536,11 @@
       </c>
       <c r="M2">
         <v>50</v>
-      </c>
-      <c r="N2" t="b">
-        <v>1</v>
       </c>
     </row>
   </sheetData>
   <dataConsolidate/>
-  <dataValidations count="12">
+  <dataValidations count="10">
     <dataValidation type="list" showInputMessage="1" showErrorMessage="1" prompt="The amount of experimental variables. This can be either 2 (Condition A, Replicates) or 3 (Condition B, Condition A, Replicates). These variables should be present in the .raw file names._x000a_Condition A example: Cell lines_x000a_Condition B example: WT/KO" sqref="B2" xr:uid="{5282C8AD-1561-44E0-A80B-84CE01E96738}">
       <formula1>"2, 3"</formula1>
     </dataValidation>
@@ -566,12 +557,6 @@
       <formula1>"protein list, specify significance, TopN"</formula1>
     </dataValidation>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="List of proteins, separated by a semiolon (;)" sqref="J2" xr:uid="{E5F7B0FE-6278-49BC-987F-F5F080EF479D}"/>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N2" xr:uid="{BFA4E188-76D8-454E-913F-287D42E85D9F}">
-      <formula1>"TRUE,FALSE"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N1" xr:uid="{05F39213-E70C-4B6E-8638-D660A08C4561}">
-      <formula1>"TRUE, FALSE"</formula1>
-    </dataValidation>
     <dataValidation type="list" showInputMessage="1" showErrorMessage="1" prompt="The type of comparison that will be tested. This can be all possible pairwise comparisons (&quot;all&quot;), a manual selection (&quot;manual&quot;) or limited to the comparisons versus the control (&quot;control&quot;)." sqref="E2" xr:uid="{CAE86A27-1E22-4258-9B9C-34B30B1C0743}">
       <formula1>"control, manual, all"</formula1>
     </dataValidation>
